--- a/artfynd/A 39868-2025 artfynd.xlsx
+++ b/artfynd/A 39868-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,61 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>68742503</v>
+        <v>82207797</v>
       </c>
       <c r="B2" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hattmyren matning, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>798770.5379152516</v>
+        <v>798771</v>
       </c>
       <c r="R2" t="n">
-        <v>7303958.338645996</v>
+        <v>7303958</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -752,22 +756,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-12-26</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-02-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-12-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-02-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,22 +781,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lars Sundberg, Lars Berggren</t>
+          <t>Lars Sundberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>82207797</v>
+        <v>69048974</v>
       </c>
       <c r="B3" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58067</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -810,16 +799,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100090</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nucifraga caryocatactes</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -833,27 +822,18 @@
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hattmyren matning, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>798770.5379152516</v>
+        <v>798771</v>
       </c>
       <c r="R3" t="n">
-        <v>7303958.338645996</v>
+        <v>7303958</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -880,22 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-02-15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-01-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-02-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-01-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,53 +885,52 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars Sundberg</t>
+          <t>Lars Sundberg, Gert Sjöberg, Kent Sjöberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105327818</v>
+        <v>90294409</v>
       </c>
       <c r="B4" t="n">
-        <v>55608</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57945</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>100110</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -974,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>798770.5379152516</v>
+        <v>798771</v>
       </c>
       <c r="R4" t="n">
-        <v>7303958.338645996</v>
+        <v>7303958</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1004,22 +973,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-12-23</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-01-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-12-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-01-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,10 +998,223 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
+          <t>Lars Sundberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>105327818</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hattmyren matning, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>798771</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7303958</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nederluleå</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-12-23</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-12-23</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lars Sundberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
           <t>Lars Sundberg, Lars Berggren</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>68742503</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hattmyren matning, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>798771</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7303958</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Nederluleå</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2017-12-26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2017-12-26</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Lars Sundberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lars Sundberg, Lars Berggren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39868-2025 artfynd.xlsx
+++ b/artfynd/A 39868-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82207797</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69048974</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90294409</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1111,6 +1131,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105327818</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1215,8 +1240,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68742503</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>